--- a/reviews/a-envoyer/otea-filmakers-2026-09-28.xlsx
+++ b/reviews/a-envoyer/otea-filmakers-2026-09-28.xlsx
@@ -886,7 +886,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-25T06:05:01</t>
+          <t>2026-09-25T10:04:50</t>
         </is>
       </c>
     </row>
